--- a/results/models/ip_v4_SA_PROMETHEE_Baseline_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
+++ b/results/models/ip_v4_SA_PROMETHEE_Baseline_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
@@ -465,11 +465,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abdurrahman Gazi Parkı</t>
+          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40.95680179214349</v>
+        <v>40.9648951717146</v>
       </c>
       <c r="E2" t="n">
-        <v>29.25999121604885</v>
+        <v>29.26242101741815</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -489,232 +489,232 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6198550457426431</v>
+        <v>0.9217709555188116</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7462630228997148</v>
+        <v>0.7900300888150814</v>
       </c>
       <c r="I2" t="n">
-        <v>3.702554851500092</v>
+        <v>4.285581690521873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ADİL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40.9648951717146</v>
+        <v>40.98072340092061</v>
       </c>
       <c r="E3" t="n">
-        <v>29.26242101741815</v>
+        <v>29.26238410907338</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9217709555188116</v>
+        <v>0.4113288785970062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7900300888150814</v>
+        <v>0.8228922971943825</v>
       </c>
       <c r="I3" t="n">
-        <v>4.285581690521873</v>
+        <v>2.829412022600539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aydos Parkı</t>
+          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>AHMET YESEVİ</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.96246645074015</v>
+        <v>40.97163567399593</v>
       </c>
       <c r="E4" t="n">
-        <v>29.25452742625226</v>
+        <v>29.26604512019534</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8255855222936668</v>
+        <v>0.8258554742137707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7021709272585134</v>
+        <v>0.7711909396521685</v>
       </c>
       <c r="I4" t="n">
-        <v>3.286399967276274</v>
+        <v>3.651632287391553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mehmet Akif Ersoy İlkokulu Bahçesi</t>
+          <t>Mevlana Parkı</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>AKŞEMSETTİN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.95553928379504</v>
+        <v>40.94874610580247</v>
       </c>
       <c r="E5" t="n">
-        <v>29.25703415059688</v>
+        <v>29.29872570873468</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9152365955831088</v>
+        <v>0.2035908471222084</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7928392367700497</v>
+        <v>0.5825983080286559</v>
       </c>
       <c r="I5" t="n">
-        <v>3.007514383478741</v>
+        <v>4.393923909287198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Belediye Fen İşleri Önü Toplanma Alanı</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>BATTALGAZİ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.98072340092061</v>
+        <v>40.98258840501005</v>
       </c>
       <c r="E6" t="n">
-        <v>29.26238410907338</v>
+        <v>29.26839981314643</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.4113288785970062</v>
+        <v>0.8816895855600266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8228922971943825</v>
+        <v>0.91927042448959</v>
       </c>
       <c r="I6" t="n">
-        <v>2.829412022600539</v>
+        <v>3.23890601448014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Muhsin Yazıcıoğlu Nikah Sarayı Önü Toplanma Alanı</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>BATTALGAZİ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40.97163567399593</v>
+        <v>40.98310901587094</v>
       </c>
       <c r="E7" t="n">
-        <v>29.26604512019534</v>
+        <v>29.27005014068656</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AHMET YESEVI</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8258554742137707</v>
+        <v>0.8755275916783325</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7711909396521685</v>
+        <v>0.886711592943929</v>
       </c>
       <c r="I7" t="n">
-        <v>3.651632287391553</v>
+        <v>3.191227715326222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mevlana Parkı</t>
+          <t>Şehit Hamit Sütmen Parkı</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>BATTALGAZİ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40.94874610580247</v>
+        <v>40.98181413193544</v>
       </c>
       <c r="E8" t="n">
-        <v>29.29872570873468</v>
+        <v>29.26881829375751</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AKSEMSETTIN</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.2035908471222084</v>
+        <v>0.5922013243750833</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5825983080286559</v>
+        <v>0.9309992901953763</v>
       </c>
       <c r="I8" t="n">
-        <v>4.393923909287198</v>
+        <v>3.286130031389185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Belediye Fen İşleri Önü Toplanma Alanı</t>
+          <t>Şehit Öğretmen Hamit Sütmen İlkokulu ve Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.98258840501005</v>
+        <v>40.98200942008475</v>
       </c>
       <c r="E9" t="n">
-        <v>29.26839981314643</v>
+        <v>29.26868471951212</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -734,92 +734,92 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8816895855600266</v>
+        <v>0.7342323393333798</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91927042448959</v>
+        <v>0.8953240933628536</v>
       </c>
       <c r="I9" t="n">
-        <v>3.23890601448014</v>
+        <v>3.274524837060275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muhsin Yazıcıoğlu Nikah Sarayı Önü Toplanma Alanı</t>
+          <t>Gölet İlkokulu Bahçesi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>FATİH</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40.98310901587094</v>
+        <v>40.95306184748708</v>
       </c>
       <c r="E10" t="n">
-        <v>29.27005014068656</v>
+        <v>29.27456122232974</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BATTALGAZI</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8755275916783325</v>
+        <v>0.5777531682581222</v>
       </c>
       <c r="H10" t="n">
-        <v>0.886711592943929</v>
+        <v>0.7125753595570942</v>
       </c>
       <c r="I10" t="n">
-        <v>3.191227715326222</v>
+        <v>4.83432850200376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gölet İlkokulu Bahçesi</t>
+          <t>İbrahim Dede Parkı</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>HAMİDİYE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40.95306184748708</v>
+        <v>40.95120838819276</v>
       </c>
       <c r="E11" t="n">
-        <v>29.27456122232974</v>
+        <v>29.2900754188337</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FATIH</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5777531682581222</v>
+        <v>0.8272125055869072</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7125753595570942</v>
+        <v>0.6818542258217239</v>
       </c>
       <c r="I11" t="n">
-        <v>4.83432850200376</v>
+        <v>5.353842274988065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>İbrahim Dede Parkı</t>
+          <t>Mevlana Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40.95120838819276</v>
+        <v>40.94972617526986</v>
       </c>
       <c r="E12" t="n">
-        <v>29.2900754188337</v>
+        <v>29.28870336682376</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8272125055869072</v>
+        <v>0.957003565127063</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6818542258217239</v>
+        <v>0.6237940206324152</v>
       </c>
       <c r="I12" t="n">
-        <v>5.353842274988065</v>
+        <v>5.454278219147464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ahmet Yener Ortaokulu Bahçesi</t>
+          <t>Hüsnü M. Özyeğin Anadolu Lisesi Bahçesi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40.96521258412454</v>
+        <v>40.97099081886383</v>
       </c>
       <c r="E13" t="n">
-        <v>29.24991319728006</v>
+        <v>29.25230054133037</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.3861822921988322</v>
+        <v>0.6335003595929511</v>
       </c>
       <c r="H13" t="n">
-        <v>0.707911693436899</v>
+        <v>0.8134050870318016</v>
       </c>
       <c r="I13" t="n">
-        <v>2.246565929038557</v>
+        <v>2.319717737621361</v>
       </c>
     </row>
     <row r="14">
@@ -1095,11 +1095,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Turgut Reis İlkokulu Bahçesi</t>
+          <t>Turgut Reis Parkı</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40.96614986801031</v>
+        <v>40.96256307543928</v>
       </c>
       <c r="E20" t="n">
-        <v>29.27966204899259</v>
+        <v>29.28139965617807</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.4575791586533158</v>
+        <v>0.03780486217219706</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7488221449191328</v>
+        <v>0.7690736177105905</v>
       </c>
       <c r="I20" t="n">
-        <v>3.099891657530684</v>
+        <v>3.929917873681156</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yaşar Paşalı İlkokulu Bahçesi</t>
+          <t>Sultanbeyli Gölet Sosyal Tesis Alanı</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40.94995917382037</v>
+        <v>40.95248348580287</v>
       </c>
       <c r="E21" t="n">
-        <v>29.27704768729355</v>
+        <v>29.27672266261231</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.7262728888101203</v>
+        <v>0.3536961253068167</v>
       </c>
       <c r="H21" t="n">
-        <v>0.549844277046868</v>
+        <v>0.6520633537370493</v>
       </c>
       <c r="I21" t="n">
-        <v>5.097536284500726</v>
+        <v>4.99567896234471</v>
       </c>
     </row>
   </sheetData>
